--- a/メンバー表.xlsx
+++ b/メンバー表.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82f6e8e916ae449b/ドキュメント/デスクトップ/pa-shift/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_AD4D066CA252ABDACC10488AA953D91073EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{949F2D37-C9C3-43F0-8E81-786F72BF36BE}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_AD4D066CA252ABDACC10488AA953D91073EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFA77F9D-631C-473A-B191-CA68F9A4860A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$21</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -97,6 +100,71 @@
     <rPh sb="0" eb="2">
       <t>ゾクセイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>りょーじ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>牟田</t>
+    <rPh sb="0" eb="2">
+      <t>ムタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>たまきち</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奏和</t>
+    <rPh sb="0" eb="1">
+      <t>カナ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もてぎ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やまと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あつや</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>だいすけ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こうしん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しゅんや</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>てらかわそう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>みくも</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -426,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -451,10 +519,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -465,13 +536,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -482,7 +550,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -499,7 +567,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -516,7 +584,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -533,19 +601,215 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7">
         <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
